--- a/outputs/comparison/biolog/BiologComparison.xlsx
+++ b/outputs/comparison/biolog/BiologComparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iYO844</t>
+          <t>iYO844_Minimal_iBsu1147</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -536,7 +536,7 @@
         <v>77</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -545,153 +545,37 @@
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.8676</v>
       </c>
       <c r="J2" t="n">
         <v>0.6667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0462</v>
+        <v>0.0484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5124</v>
+        <v>0.4334</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9538</v>
+        <v>0.9516</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.8676</v>
       </c>
       <c r="O2" t="n">
         <v>0.6667</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9323</v>
+        <v>0.9077</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8831</v>
+        <v>0.8442</v>
       </c>
       <c r="R2" t="n">
         <v>2.3854</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>iBB1018</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>214</v>
-      </c>
-      <c r="C3" t="n">
-        <v>96</v>
-      </c>
-      <c r="D3" t="n">
-        <v>77</v>
-      </c>
-      <c r="E3" t="n">
-        <v>68</v>
-      </c>
-      <c r="F3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.1169</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.8831</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.9379</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.8831</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.2292</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>iBsu1147R</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>254</v>
-      </c>
-      <c r="C4" t="n">
-        <v>96</v>
-      </c>
-      <c r="D4" t="n">
-        <v>75</v>
-      </c>
-      <c r="E4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8615</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2349</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.9032</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8615</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.8819</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.6458</v>
       </c>
     </row>
   </sheetData>
